--- a/Result/profitability/3188.xlsx
+++ b/Result/profitability/3188.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.88875</v>
+        <v>0.94125</v>
       </c>
       <c r="N2" t="n">
-        <v>45.90375</v>
+        <v>43.9475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>0.87125</v>
+        <v>0.99</v>
       </c>
       <c r="N3" t="n">
-        <v>43.1025</v>
+        <v>41.29499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0.86375</v>
+        <v>0.9812500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>40.34999999999999</v>
+        <v>38.645</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.80625</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>37.99</v>
+        <v>37.09</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7525000000000001</v>
+        <v>0.5750000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>35.17375</v>
+        <v>34.12625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3775000000000001</v>
+        <v>0.3825</v>
       </c>
       <c r="N7" t="n">
-        <v>32.45999999999999</v>
+        <v>31.9575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2275</v>
+        <v>0.09249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>30.99625</v>
+        <v>30.78625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9770,6 +9770,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>927</v>
+      </c>
+      <c r="D75" t="n">
+        <v>575</v>
+      </c>
+      <c r="E75" t="n">
+        <v>352</v>
+      </c>
+      <c r="F75" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="G75" t="n">
+        <v>279</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>30.07%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>278</v>
+      </c>
+      <c r="K75" t="n">
+        <v>219</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N75" t="n">
+        <v>46.09875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4821428571428572</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04237074401008822</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7.923076923076922</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.200000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1593978304184194</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
